--- a/etf_holdings/2026-10-14_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:05</t>
+          <t>2026-10-14 00:25:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:07</t>
+          <t>2026-10-14 00:25:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:08</t>
+          <t>2026-10-14 00:25:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:09</t>
+          <t>2026-10-14 00:25:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:09</t>
+          <t>2026-10-14 00:25:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:09</t>
+          <t>2026-10-14 00:25:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:09</t>
+          <t>2026-10-14 00:25:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:09</t>
+          <t>2026-10-14 00:25:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 00:09:09</t>
+          <t>2026-10-14 00:25:33</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-10-14_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:29</t>
+          <t>2026-10-14 00:59:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:30</t>
+          <t>2026-10-14 00:59:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:31</t>
+          <t>2026-10-14 00:59:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:33</t>
+          <t>2026-10-14 00:59:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:33</t>
+          <t>2026-10-14 00:59:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:33</t>
+          <t>2026-10-14 00:59:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:33</t>
+          <t>2026-10-14 00:59:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:33</t>
+          <t>2026-10-14 00:59:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:33</t>
+          <t>2026-10-14 00:59:51</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-10-14_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00403A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.81%7,700,000</t>
+          <t>13.75%7,700,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.81%</t>
+          <t>13.75%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4525</v>
+        <v>4475</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.35%1,950,000</t>
+          <t>6.26%1,950,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.35%</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.98%1180</t>
+          <t>+0.42%1185</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.37%6990</t>
+          <t>+1.14%7070</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6990</v>
+        <v>7070</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.61%1,115,000</t>
+          <t>5.65%1,115,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.61%</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5545</v>
+        <v>5520</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.59%1,400,000</t>
+          <t>5.54%1,400,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>5.54%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3280</v>
+        <v>3315</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.96%2,100,000</t>
+          <t>4.99%2,100,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.96%</t>
+          <t>4.99%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.1%5940</t>
+          <t>+4.67%627</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5940</v>
+        <v>627</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.98%930,000</t>
+          <t>3.96%8,800,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.98%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>930000</v>
+        <v>8800000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-5.82%599</t>
+          <t>-0.93%5885</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>599</v>
+        <v>5885</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.80%8,800,000</t>
+          <t>3.93%930,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8800000</v>
+        <v>930000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,33 +997,33 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.06%8095</t>
+          <t>+1.85%8245</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8095</v>
+        <v>8245</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.73%640,000</t>
+          <t>3.87%655,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>640000</v>
+        <v>655000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.58%1775</t>
+          <t>+0.56%1785</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.58%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1775</v>
+        <v>1785</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.89%1040</t>
+          <t>+0.96%1050</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.33%4,450,000</t>
+          <t>3.35%4,450,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0%1440</t>
+          <t>-0.69%1430</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.12%3,010,000</t>
+          <t>3.09%3,010,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-3.52%2195</t>
+          <t>+9.4%349</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>+9.4%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2195</v>
+        <v>349</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.68%1,697,956</t>
+          <t>2.88%11,500,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1697956</v>
+        <v>11500000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,34 +1297,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+5.28%319</t>
+          <t>+4.83%1735</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+5.28%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>319</v>
+        <v>1735</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.64%11,500,000</t>
+          <t>2.71%2,180,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>11500000</v>
+        <v>2180000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:47</t>
+          <t>2026-10-14 21:53:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-4.61%1655</t>
+          <t>-3.64%2115</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-4.61%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1655</v>
+        <v>2115</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.50%2,100,000</t>
+          <t>2.58%1,697,956</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2100000</v>
+        <v>1697956</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-4.03%2260</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-4.03%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2260</v>
+        <v>2050</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.38%1,460,000</t>
+          <t>2.35%1,600,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1460000</v>
+        <v>1600000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.23%2040</t>
+          <t>-1.11%2235</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2040</v>
+        <v>2235</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.35%1,600,000</t>
+          <t>2.34%1,460,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1600000</v>
+        <v>1460000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.29%1715</t>
+          <t>-1.75%1685</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1715</v>
+        <v>1685</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.32%1,880,000</t>
+          <t>2.27%1,880,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.75%141.5</t>
+          <t>+0.86%17500</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>141.5</v>
+        <v>17500</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.04%20,000,000</t>
+          <t>1.83%145,500</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>20000000</v>
+        <v>145500</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.68%7275</t>
+          <t>-5.43%6880</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7275</v>
+        <v>6880</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.75%335,000</t>
+          <t>1.65%335,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.95%17350</t>
+          <t>+0.35%142</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>17350</v>
+        <v>142</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.47%117,500</t>
+          <t>1.53%15,000,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>117500</v>
+        <v>15000000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-7.4%488</t>
+          <t>-1.54%480.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>488</v>
+        <v>480.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.98%2,800,000</t>
+          <t>0.97%2,800,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.67%305</t>
+          <t>-2.79%296.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>305</v>
+        <v>296.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.88%4,000,000</t>
+          <t>0.85%4,000,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.84%240</t>
+          <t>+1.25%243</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.55%3,200,000</t>
+          <t>0.56%3,200,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.91%10060</t>
+          <t>-0.55%10005</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>10060</v>
+        <v>10005</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3211順達</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-5.62%361</t>
+          <t>+5.71%500</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.62%</t>
+          <t>+5.71%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>361</v>
+        <v>500</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.52%2,000,000</t>
+          <t>0.54%1,500,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>3211順達</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-8.86%473</t>
+          <t>0%361</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.86%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>473</v>
+        <v>361</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.51%1,500,000</t>
+          <t>0.52%2,000,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1500000</v>
+        <v>2000000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-5.51%1630</t>
+          <t>+7.69%1260</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.51%</t>
+          <t>+7.69%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1630</v>
+        <v>1260</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.41%350,000</t>
+          <t>0.43%480,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>350000</v>
+        <v>480000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-5.96%710</t>
+          <t>+0.61%1640</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.96%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>710</v>
+        <v>1640</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.41%800,000</t>
+          <t>0.41%350,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>800000</v>
+        <v>350000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:48</t>
+          <t>2026-10-14 21:53:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-5.26%1170</t>
+          <t>+0.14%711</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1170</v>
+        <v>711</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.40%480,000</t>
+          <t>0.41%800,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>480000</v>
+        <v>800000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.33%114.5</t>
+          <t>-0.44%114</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>114.5</v>
+        <v>114</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.64%2210</t>
+          <t>-0.68%2195</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2210</v>
+        <v>2195</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-8.97%1015</t>
+          <t>+0.49%1020</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.97%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-3.37%243.5</t>
+          <t>+2.87%250.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-3.37%</t>
+          <t>+2.87%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>243.5</v>
+        <v>250.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.21%1,200,000</t>
+          <t>0.22%1,200,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-5%950</t>
+          <t>-0.21%948</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2481強茂</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-5.26%162</t>
+          <t>+2.95%523</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+2.95%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>162</v>
+        <v>523</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.08%700,000</t>
+          <t>0.08%200,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>700000</v>
+        <v>200000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-9.93%508</t>
+          <t>+2.64%253</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-9.93%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>508</v>
+        <v>253</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.07%200,000</t>
+          <t>0.06%350,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>200000</v>
+        <v>350000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,25 +2761,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-6.45%246.5</t>
+          <t>+2.54%283</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-6.45%</t>
+          <t>+2.54%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>246.5</v>
+        <v>283</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.06%350,000</t>
+          <t>0.06%300,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>1717長興</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.17%276</t>
+          <t>+3.28%75.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.17%</t>
+          <t>+3.28%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>276</v>
+        <v>75.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.06%300,000</t>
+          <t>0.05%900,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>300000</v>
+        <v>900000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1717長興</t>
+          <t>2481強茂</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.14%73.1</t>
+          <t>+2.47%166</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>+2.47%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>73.09999999999999</v>
+        <v>166</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.05%900,000</t>
+          <t>0.04%350,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>900000</v>
+        <v>350000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.47%268.5</t>
+          <t>+3.54%278</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+3.54%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>268.5</v>
+        <v>278</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-5.56%493</t>
+          <t>+1.83%502</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-4.38%1965</t>
+          <t>0%1965</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-4.38%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.44%641</t>
+          <t>+2.34%656</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.44%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:49</t>
+          <t>2026-10-14 21:53:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.79%296</t>
+          <t>+0.84%298.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>296</v>
+        <v>298.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:51</t>
+          <t>2026-10-14 21:53:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-3.25%327</t>
+          <t>+1.83%333</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.25%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:51</t>
+          <t>2026-10-14 21:53:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-6.98%2200</t>
+          <t>+2.27%2250</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:51</t>
+          <t>2026-10-14 21:53:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-7.69%1140</t>
+          <t>+1.32%1155</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-7.69%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1140</v>
+        <v>1155</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:51</t>
+          <t>2026-10-14 21:53:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-6.47%6070</t>
+          <t>+2.17%165</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-6.47%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>6070</v>
+        <v>165</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:51</t>
+          <t>2026-10-14 21:53:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,21 +3493,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-7.18%161.5</t>
+          <t>+0.95%747</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-7.18%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>161.5</v>
+        <v>747</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3528,67 +3528,6 @@
         </is>
       </c>
       <c r="M51" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-10-14 00:59:51</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>3711日月光投控</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-2.89%740</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-2.89%</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>740</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>0%1,000</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-14_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:46</t>
+          <t>2026-10-14 22:01:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:49</t>
+          <t>2026-10-14 22:01:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:50</t>
+          <t>2026-10-14 22:01:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:51</t>
+          <t>2026-10-14 22:01:29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:51</t>
+          <t>2026-10-14 22:01:29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:51</t>
+          <t>2026-10-14 22:01:29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:51</t>
+          <t>2026-10-14 22:01:29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:51</t>
+          <t>2026-10-14 22:01:29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:25</t>
+          <t>2026-10-14 22:31:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:27</t>
+          <t>2026-10-14 22:31:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:28</t>
+          <t>2026-10-14 22:31:34</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:29</t>
+          <t>2026-10-14 22:31:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:29</t>
+          <t>2026-10-14 22:31:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:29</t>
+          <t>2026-10-14 22:31:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:29</t>
+          <t>2026-10-14 22:31:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:29</t>
+          <t>2026-10-14 22:31:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
